--- a/web-app/templates/telecalling-lead-audit.xlsx
+++ b/web-app/templates/telecalling-lead-audit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns10="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:ns6="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gurupunvaanii.sharepoint.com/sites/GPPRepository/Shared Documents/GPP Backend Ops/Marketing/Lead Audit/"/>
+      <ns2:absPath url="https://gurupunvaanii.sharepoint.com/sites/GPPRepository/Shared Documents/GPP Backend Ops/Marketing/Lead Audit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{5D017B0D-B322-450B-A02F-6660CBF850EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{001081BA-8F5D-4785-9555-575D1B3EF94B}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{5D017B0D-B322-450B-A02F-6660CBF850EB}" ns4:coauthVersionLast="47" ns4:coauthVersionMax="47" ns5:uidLastSave="{001081BA-8F5D-4785-9555-575D1B3EF94B}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1230" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1230" windowWidth="29040" windowHeight="15720" activeTab="1" ns6:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="2" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Telecaller Performance" sheetId="4" r:id="rId4"/>
     <sheet name="Graphical Dashboard" sheetId="5" r:id="rId5"/>
     <sheet name="Detailed Error Report" sheetId="6" r:id="rId6"/>
+    <sheet name="ChartCache" sheetId="7" state="veryHidden" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="Slicer_Error_Type">#N/A</definedName>
@@ -27,13 +28,13 @@
     <definedName name="Slicer_Severity">#N/A</definedName>
     <definedName name="Slicer_Telecaller_Name">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+    <ext uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{46BE6895-7355-4a93-B00E-2C351335B9C9}">
-      <x15:slicerCaches xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
+    <ext uri="{46BE6895-7355-4a93-B00E-2C351335B9C9}">
+      <x15:slicerCaches>
         <x14:slicerCache r:id="rId7"/>
         <x14:slicerCache r:id="rId8"/>
         <x14:slicerCache r:id="rId9"/>
@@ -41,16 +42,16 @@
         <x14:slicerCache r:id="rId11"/>
       </x15:slicerCaches>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <ns10:calcFeatures>
+        <ns10:feature name="microsoft.com:RD"/>
+        <ns10:feature name="microsoft.com:Single"/>
+        <ns10:feature name="microsoft.com:FV"/>
+        <ns10:feature name="microsoft.com:CNMTM"/>
+        <ns10:feature name="microsoft.com:LET_WF"/>
+        <ns10:feature name="microsoft.com:LAMBDA_WF"/>
+        <ns10:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </ns10:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -79,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="148">
   <si>
     <t>Project Name</t>
   </si>
@@ -521,6 +522,9 @@
   <si>
     <t>Start with critical classification and overdue follow-up errors, then review customer-location capture for Ernika, Exotica, and EKA. Use the Detailed Error Report filters for coaching evidence.</t>
   </si>
+  <si>
+    <t>RowVis</t>
+  </si>
 </sst>
 </file>
 
@@ -529,7 +533,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="dd/mmm/yyyy"/>
     <numFmt numFmtId="165" formatCode="dd/mmm/yyyy\ hh:mm"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.00%"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -856,7 +860,7 @@
       <alignment wrapText="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <numFmt numFmtId="166" formatCode="0.00%"/>
       <alignment wrapText="0"/>
     </dxf>
     <dxf>
@@ -1029,12 +1033,9 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Raw Data'!$X$1</c:f>
+              <c:f>ChartCache!$B$1</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Accuracy</c:v>
-                </c:pt>
+                <c:ptCount val="0"/>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -1108,42 +1109,18 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Raw Data'!$W$2:$W$5</c:f>
+              <c:f>ChartCache!$A$2:$A$51</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Prathima Hegde</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Vinutha M1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Amulya P</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Manoj Vs 1</c:v>
-                </c:pt>
+                <c:ptCount val="0"/>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Raw Data'!$X$2:$X$5</c:f>
+              <c:f>ChartCache!$B$2:$B$51</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.2142857142857143</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="0"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1280,7 +1257,7 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:plotVisOnly val="0"/>
+    <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
     <c:extLst>
@@ -1405,12 +1382,9 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Raw Data'!$AA$1</c:f>
+              <c:f>ChartCache!$E$1</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Errors</c:v>
-                </c:pt>
+                <c:ptCount val="0"/>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -1484,42 +1458,18 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Raw Data'!$Z$2:$Z$5</c:f>
+              <c:f>ChartCache!$D$2:$D$51</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Prathima Hegde</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Vinutha M1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Amulya P</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Manoj Vs 1</c:v>
-                </c:pt>
+                <c:ptCount val="0"/>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Raw Data'!$AA$2:$AA$5</c:f>
+              <c:f>ChartCache!$E$2:$E$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3</c:v>
-                </c:pt>
+                <c:ptCount val="0"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1657,7 +1607,7 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:plotVisOnly val="0"/>
+    <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
     <c:extLst>
@@ -1780,12 +1730,9 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Raw Data'!$AD$1</c:f>
+              <c:f>ChartCache!$H$1</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Count</c:v>
-                </c:pt>
+                <c:ptCount val="0"/>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -1989,60 +1936,18 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Raw Data'!$AC$2:$AC$8</c:f>
+              <c:f>ChartCache!$G$2:$G$51</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>Wrong Lead Status</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Cold Status Mismatch</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Warm Status Mismatch</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>RNR Classification Error</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Follow-up Error</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>CRM Status Mismatch</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Customer Location Not Captured</c:v>
-                </c:pt>
+                <c:ptCount val="0"/>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Raw Data'!$AD$2:$AD$8</c:f>
+              <c:f>ChartCache!$H$2:$H$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>17</c:v>
-                </c:pt>
+                <c:ptCount val="0"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2102,7 +2007,7 @@
         </a:p>
       </c:txPr>
     </c:legend>
-    <c:plotVisOnly val="0"/>
+    <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
     <c:extLst>
@@ -2227,12 +2132,9 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Raw Data'!$AG$1</c:f>
+              <c:f>ChartCache!$K$1</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Errors</c:v>
-                </c:pt>
+                <c:ptCount val="0"/>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -2306,48 +2208,18 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Raw Data'!$AF$2:$AF$6</c:f>
+              <c:f>ChartCache!$J$2:$J$51</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Guru Punvaanii EKA</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Guru Punvaanii Elegance</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Guru Punvaanii Ernika</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Guru Punvaanii Eureka</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Guru Punvaanii Shyam Residency</c:v>
-                </c:pt>
+                <c:ptCount val="0"/>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Raw Data'!$AG$2:$AG$6</c:f>
+              <c:f>ChartCache!$K$2:$K$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3</c:v>
-                </c:pt>
+                <c:ptCount val="0"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2485,7 +2357,7 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:plotVisOnly val="0"/>
+    <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
     <c:extLst>
@@ -2608,12 +2480,9 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Raw Data'!$AJ$1</c:f>
+              <c:f>ChartCache!$N$1</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Count</c:v>
-                </c:pt>
+                <c:ptCount val="0"/>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -2735,36 +2604,18 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Raw Data'!$AI$2:$AI$4</c:f>
+              <c:f>ChartCache!$M$2:$M$51</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Critical</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Medium</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Low</c:v>
-                </c:pt>
+                <c:ptCount val="0"/>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Raw Data'!$AJ$2:$AJ$4</c:f>
+              <c:f>ChartCache!$N$2:$N$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
+                <c:ptCount val="0"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2825,7 +2676,7 @@
         </a:p>
       </c:txPr>
     </c:legend>
-    <c:plotVisOnly val="0"/>
+    <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
     <c:extLst>
@@ -6254,9 +6105,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C97253A4-792D-4D3B-B2B5-FC48F86C840F}" name="RawData" displayName="RawData" ref="A1:U37" totalsRowShown="0">
-  <autoFilter ref="A1:U37" xr:uid="{C97253A4-792D-4D3B-B2B5-FC48F86C840F}"/>
-  <tableColumns count="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C97253A4-792D-4D3B-B2B5-FC48F86C840F}" name="RawData" displayName="RawData" ref="A1:V2" totalsRowShown="0">
+  <autoFilter ref="A1:V2" xr:uid="{C97253A4-792D-4D3B-B2B5-FC48F86C840F}"/>
+  <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{59D34C9F-57CE-46B2-A272-A1EFAF9C5198}" name="Project Name"/>
     <tableColumn id="2" xr3:uid="{5113F6D5-6A6D-47EB-AE4E-6CE383A7E8C3}" name="Mobile" dataDxfId="36"/>
     <tableColumn id="3" xr3:uid="{4E86AD45-088C-4D5F-ABE8-F7F004FDAB23}" name="Telecaller Name"/>
@@ -6272,23 +6123,14 @@
     <tableColumn id="13" xr3:uid="{7C4E37D4-7C3F-454F-A7EB-B3F2B8FECA74}" name="Source"/>
     <tableColumn id="14" xr3:uid="{1580CB3F-E30E-4CE2-B5E0-0EE5C37D3DA4}" name="Source Name"/>
     <tableColumn id="15" xr3:uid="{5A88AB69-D316-4C4C-A395-55C689FACF19}" name="Totals"/>
-    <tableColumn id="16" xr3:uid="{325B0B7A-4678-4FF2-88FF-679012D8ED18}" name="Error Type" dataDxfId="32">
-      <calculatedColumnFormula>IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="17" xr3:uid="{6F399763-7A6E-4AE0-884A-1E4BB6970DFA}" name="Error Details" dataDxfId="31">
-      <calculatedColumnFormula>IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="18" xr3:uid="{10A8C431-FF2A-401D-8C5D-23A89B988D63}" name="Recommended Action" dataDxfId="30">
-      <calculatedColumnFormula>IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="19" xr3:uid="{E811C850-BB86-4EF4-92A4-54DD656219F7}" name="Severity" dataDxfId="29">
-      <calculatedColumnFormula>IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="20" xr3:uid="{AD6A0625-A74D-44DC-9BB1-7EABEE0AC0E1}" name="Audit Status" dataDxfId="28">
-      <calculatedColumnFormula>IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="21" xr3:uid="{BEA88A10-2BC3-440C-8D2D-7C95FF77BB9A}" name="Error Flag" dataDxfId="27">
-      <calculatedColumnFormula>IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</calculatedColumnFormula>
+    <tableColumn id="16" xr3:uid="{325B0B7A-4678-4FF2-88FF-679012D8ED18}" name="Error Type" dataDxfId="32"/>
+    <tableColumn id="17" xr3:uid="{6F399763-7A6E-4AE0-884A-1E4BB6970DFA}" name="Error Details" dataDxfId="31"/>
+    <tableColumn id="18" xr3:uid="{10A8C431-FF2A-401D-8C5D-23A89B988D63}" name="Recommended Action" dataDxfId="30"/>
+    <tableColumn id="19" xr3:uid="{E811C850-BB86-4EF4-92A4-54DD656219F7}" name="Severity" dataDxfId="29"/>
+    <tableColumn id="20" xr3:uid="{AD6A0625-A74D-44DC-9BB1-7EABEE0AC0E1}" name="Audit Status" dataDxfId="28"/>
+    <tableColumn id="21" xr3:uid="{BEA88A10-2BC3-440C-8D2D-7C95FF77BB9A}" name="Error Flag" dataDxfId="27"/>
+    <tableColumn id="22" xr3:uid="{B4641721-C7B9-4F1D-BF7B-4048F631BBC3}" name="RowVis">
+      <calculatedColumnFormula>SUBTOTAL(103,RawData[[#This Row],[Mobile]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6806,8 +6648,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ200"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.125" bestFit="1" customWidth="1"/>
@@ -6826,9 +6668,10 @@
     <col min="17" max="17" width="9.875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13.875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6892,18 +6735,6 @@
       <c r="U1" t="s">
         <v>93</v>
       </c>
-      <c r="V1" t="s">
-        <v>135</v>
-      </c>
-      <c r="W1" t="s">
-        <v>134</v>
-      </c>
-      <c r="X1" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>134</v>
-      </c>
       <c r="AA1" t="s">
         <v>136</v>
       </c>
@@ -6925,3532 +6756,11 @@
       <c r="AJ1" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="1">
-        <v>7899415022</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="2">
-        <v>46254</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="3">
-        <v>46256.458333333336</v>
-      </c>
-      <c r="I2" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v/>
-      </c>
-      <c r="R2" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v/>
-      </c>
-      <c r="S2" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v/>
-      </c>
-      <c r="T2" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Pass</v>
-      </c>
-      <c r="U2" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>0</v>
-      </c>
-      <c r="W2" t="str">
-        <f ca="1">'Telecaller Performance'!A6</f>
-        <v>Prathima Hegde</v>
-      </c>
-      <c r="X2" s="8" cm="1">
-        <f t="array" aca="1" ref="X2" ca="1">IF(W2="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W2)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W2),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>1</v>
-      </c>
-      <c r="Z2" t="str">
-        <f ca="1">'Telecaller Performance'!A6</f>
-        <v>Prathima Hegde</v>
-      </c>
-      <c r="AA2" cm="1">
-        <f t="array" aca="1" ref="AA2" ca="1">IF(Z2="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z2)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z2),RawData[Error Flag]))))</f>
-        <v>0</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>127</v>
-      </c>
-      <c r="AD2" cm="1">
-        <f t="array" aca="1" ref="AD2" ca="1">_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),SUMPRODUCT(_xlpm.v,--ISNUMBER(SEARCH(AC2,RawData[Error Type]))))</f>
-        <v>3</v>
-      </c>
-      <c r="AF2" t="str" cm="1">
-        <f t="array" ref="AF2">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF2)),"")</f>
-        <v>Guru Punvaanii EKA</v>
-      </c>
-      <c r="AG2" cm="1">
-        <f t="array" aca="1" ref="AG2" ca="1">IF(AF2="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF2)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF2),RawData[Error Flag]))))</f>
-        <v>1</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ2" cm="1">
-        <f t="array" aca="1" ref="AJ2" ca="1">_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),SUMPRODUCT(_xlpm.v,--ISNUMBER(SEARCH("Wrong Lead Status",RawData[Error Type])))+SUMPRODUCT(_xlpm.v,--ISNUMBER(SEARCH("RNR Classification Error",RawData[Error Type])))+SUMPRODUCT(_xlpm.v,--ISNUMBER(SEARCH("Follow-up Error",RawData[Error Type]))))</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="1">
-        <v>8861583888</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="3">
-        <v>46256.495138888888</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" t="s">
-        <v>15</v>
-      </c>
-      <c r="N3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Customer Location Not Captured</v>
-      </c>
-      <c r="Q3" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Anekal is the project default; customer location was not captured</v>
-      </c>
-      <c r="R3" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Contact the customer and record their actual location</v>
-      </c>
-      <c r="S3" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Medium</v>
-      </c>
-      <c r="T3" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U3" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-      <c r="W3" t="str">
-        <f ca="1">'Telecaller Performance'!A7</f>
-        <v>Vinutha M1</v>
-      </c>
-      <c r="X3" s="8" cm="1">
-        <f t="array" aca="1" ref="X3" ca="1">IF(W3="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W3)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W3),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>0.2142857142857143</v>
-      </c>
-      <c r="Z3" t="str">
-        <f ca="1">'Telecaller Performance'!A7</f>
-        <v>Vinutha M1</v>
-      </c>
-      <c r="AA3" cm="1">
-        <f t="array" aca="1" ref="AA3" ca="1">IF(Z3="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z3)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z3),RawData[Error Flag]))))</f>
-        <v>22</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>128</v>
-      </c>
-      <c r="AD3" cm="1">
-        <f t="array" aca="1" ref="AD3" ca="1">_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),SUMPRODUCT(_xlpm.v,--ISNUMBER(SEARCH(AC3,RawData[Error Type]))))</f>
-        <v>0</v>
-      </c>
-      <c r="AF3" t="str" cm="1">
-        <f t="array" ref="AF3">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF3)),"")</f>
-        <v>Guru Punvaanii Elegance</v>
-      </c>
-      <c r="AG3" cm="1">
-        <f t="array" aca="1" ref="AG3" ca="1">IF(AF3="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF3)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF3),RawData[Error Flag]))))</f>
-        <v>1</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>139</v>
-      </c>
-      <c r="AJ3" cm="1">
-        <f t="array" aca="1" ref="AJ3" ca="1">_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),SUMPRODUCT(_xlpm.v,--ISNUMBER(SEARCH("Warm Status Mismatch",RawData[Error Type])))+SUMPRODUCT(_xlpm.v,--ISNUMBER(SEARCH("CRM Status Mismatch",RawData[Error Type])))+SUMPRODUCT(_xlpm.v,--ISNUMBER(SEARCH("Customer Location Not Captured",RawData[Error Type]))))</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="1">
-        <v>9513809427</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="3">
-        <v>46256.465277777781</v>
-      </c>
-      <c r="I4" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v/>
-      </c>
-      <c r="R4" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v/>
-      </c>
-      <c r="S4" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v/>
-      </c>
-      <c r="T4" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Pass</v>
-      </c>
-      <c r="U4" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>0</v>
-      </c>
-      <c r="W4" t="str">
-        <f ca="1">'Telecaller Performance'!A8</f>
-        <v>Amulya P</v>
-      </c>
-      <c r="X4" s="8" cm="1">
-        <f t="array" aca="1" ref="X4" ca="1">IF(W4="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W4)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W4),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>0.5</v>
-      </c>
-      <c r="Z4" t="str">
-        <f ca="1">'Telecaller Performance'!A8</f>
-        <v>Amulya P</v>
-      </c>
-      <c r="AA4" cm="1">
-        <f t="array" aca="1" ref="AA4" ca="1">IF(Z4="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z4)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z4),RawData[Error Flag]))))</f>
-        <v>2</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>129</v>
-      </c>
-      <c r="AD4" cm="1">
-        <f t="array" aca="1" ref="AD4" ca="1">_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),SUMPRODUCT(_xlpm.v,--ISNUMBER(SEARCH(AC4,RawData[Error Type]))))</f>
-        <v>2</v>
-      </c>
-      <c r="AF4" t="str" cm="1">
-        <f t="array" ref="AF4">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF4)),"")</f>
-        <v>Guru Punvaanii Ernika</v>
-      </c>
-      <c r="AG4" cm="1">
-        <f t="array" aca="1" ref="AG4" ca="1">IF(AF4="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF4)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF4),RawData[Error Flag]))))</f>
-        <v>21</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>140</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="1">
-        <v>9972515173</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="2">
-        <v>46254</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="3">
-        <v>46255.484027777777</v>
-      </c>
-      <c r="H5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="4">
-        <v>0</v>
-      </c>
-      <c r="J5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" t="s">
-        <v>35</v>
-      </c>
-      <c r="N5" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Follow-up Error</v>
-      </c>
-      <c r="Q5" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Follow-up date/time has passed for an active lead</v>
-      </c>
-      <c r="R5" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Contact immediately and set the next follow-up</v>
-      </c>
-      <c r="S5" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Critical</v>
-      </c>
-      <c r="T5" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U5" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-      <c r="W5" t="str">
-        <f ca="1">'Telecaller Performance'!A9</f>
-        <v>Manoj Vs 1</v>
-      </c>
-      <c r="X5" s="8" cm="1">
-        <f t="array" aca="1" ref="X5" ca="1">IF(W5="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W5)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W5),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>0</v>
-      </c>
-      <c r="Z5" t="str">
-        <f ca="1">'Telecaller Performance'!A9</f>
-        <v>Manoj Vs 1</v>
-      </c>
-      <c r="AA5" cm="1">
-        <f t="array" aca="1" ref="AA5" ca="1">IF(Z5="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z5)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z5),RawData[Error Flag]))))</f>
-        <v>3</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>130</v>
-      </c>
-      <c r="AD5" cm="1">
-        <f t="array" aca="1" ref="AD5" ca="1">_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),SUMPRODUCT(_xlpm.v,--ISNUMBER(SEARCH(AC5,RawData[Error Type]))))</f>
-        <v>3</v>
-      </c>
-      <c r="AF5" t="str" cm="1">
-        <f t="array" ref="AF5">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF5)),"")</f>
-        <v>Guru Punvaanii Eureka</v>
-      </c>
-      <c r="AG5" cm="1">
-        <f t="array" aca="1" ref="AG5" ca="1">IF(AF5="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF5)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF5),RawData[Error Flag]))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="1">
-        <v>6361095505</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="2">
-        <v>46254</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="3">
-        <v>46256.493750000001</v>
-      </c>
-      <c r="H6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" t="s">
-        <v>38</v>
-      </c>
-      <c r="N6" t="s">
-        <v>39</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Customer Location Not Captured</v>
-      </c>
-      <c r="Q6" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Anekal is the project default; customer location was not captured</v>
-      </c>
-      <c r="R6" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Contact the customer and record their actual location</v>
-      </c>
-      <c r="S6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Medium</v>
-      </c>
-      <c r="T6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U6" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-      <c r="W6" t="str">
-        <f ca="1">'Telecaller Performance'!A10</f>
-        <v/>
-      </c>
-      <c r="X6" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X6" ca="1">IF(W6="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W6)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W6),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z6" t="str">
-        <f ca="1">'Telecaller Performance'!A10</f>
-        <v/>
-      </c>
-      <c r="AA6" t="e" cm="1">
-        <f t="array" aca="1" ref="AA6" ca="1">IF(Z6="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z6)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z6),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>131</v>
-      </c>
-      <c r="AD6" cm="1">
-        <f t="array" aca="1" ref="AD6" ca="1">_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),SUMPRODUCT(_xlpm.v,--ISNUMBER(SEARCH(AC6,RawData[Error Type]))))</f>
-        <v>2</v>
-      </c>
-      <c r="AF6" t="str" cm="1">
-        <f t="array" ref="AF6">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF6)),"")</f>
-        <v>Guru Punvaanii Shyam Residency</v>
-      </c>
-      <c r="AG6" cm="1">
-        <f t="array" aca="1" ref="AG6" ca="1">IF(AF6="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF6)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF6),RawData[Error Flag]))))</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="1">
-        <v>7019359269</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="3">
-        <v>46256.427083333336</v>
-      </c>
-      <c r="H7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" t="s">
-        <v>38</v>
-      </c>
-      <c r="N7" t="s">
-        <v>39</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Customer Location Not Captured</v>
-      </c>
-      <c r="Q7" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Anekal is the project default; customer location was not captured</v>
-      </c>
-      <c r="R7" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Contact the customer and record their actual location</v>
-      </c>
-      <c r="S7" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Medium</v>
-      </c>
-      <c r="T7" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U7" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-      <c r="W7" t="str">
-        <f ca="1">'Telecaller Performance'!A11</f>
-        <v/>
-      </c>
-      <c r="X7" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X7" ca="1">IF(W7="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W7)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W7),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z7" t="str">
-        <f ca="1">'Telecaller Performance'!A11</f>
-        <v/>
-      </c>
-      <c r="AA7" t="e" cm="1">
-        <f t="array" aca="1" ref="AA7" ca="1">IF(Z7="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z7)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z7),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>132</v>
-      </c>
-      <c r="AD7" cm="1">
-        <f t="array" aca="1" ref="AD7" ca="1">_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),SUMPRODUCT(_xlpm.v,--ISNUMBER(SEARCH(AC7,RawData[Error Type]))))</f>
-        <v>0</v>
-      </c>
-      <c r="AF7" t="str" cm="1">
-        <f t="array" ref="AF7">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG7" t="e" cm="1">
-        <f t="array" aca="1" ref="AG7" ca="1">IF(AF7="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF7)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF7),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="1">
-        <v>7406119929</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="3">
-        <v>46256.435416666667</v>
-      </c>
-      <c r="H8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8" t="s">
-        <v>27</v>
-      </c>
-      <c r="M8" t="s">
-        <v>38</v>
-      </c>
-      <c r="N8" t="s">
-        <v>39</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Customer Location Not Captured</v>
-      </c>
-      <c r="Q8" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Anekal is the project default; customer location was not captured</v>
-      </c>
-      <c r="R8" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Contact the customer and record their actual location</v>
-      </c>
-      <c r="S8" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Medium</v>
-      </c>
-      <c r="T8" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U8" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-      <c r="W8" t="str">
-        <f ca="1">'Telecaller Performance'!A12</f>
-        <v/>
-      </c>
-      <c r="X8" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X8" ca="1">IF(W8="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W8)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W8),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z8" t="str">
-        <f ca="1">'Telecaller Performance'!A12</f>
-        <v/>
-      </c>
-      <c r="AA8" t="e" cm="1">
-        <f t="array" aca="1" ref="AA8" ca="1">IF(Z8="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z8)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z8),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>144</v>
-      </c>
-      <c r="AD8" cm="1">
-        <f t="array" aca="1" ref="AD8" ca="1">_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),SUMPRODUCT(_xlpm.v,--ISNUMBER(SEARCH(AC8,RawData[Error Type]))))</f>
-        <v>17</v>
-      </c>
-      <c r="AF8" t="str" cm="1">
-        <f t="array" ref="AF8">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF8)),"")</f>
-        <v/>
-      </c>
-      <c r="AG8" t="e" cm="1">
-        <f t="array" aca="1" ref="AG8" ca="1">IF(AF8="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF8)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF8),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="1">
-        <v>7795505658</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="3">
-        <v>46256.469444444447</v>
-      </c>
-      <c r="H9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" t="s">
-        <v>41</v>
-      </c>
-      <c r="M9" t="s">
-        <v>38</v>
-      </c>
-      <c r="N9" t="s">
-        <v>39</v>
-      </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Customer Location Not Captured</v>
-      </c>
-      <c r="Q9" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Anekal is the project default; customer location was not captured</v>
-      </c>
-      <c r="R9" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Contact the customer and record their actual location</v>
-      </c>
-      <c r="S9" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Medium</v>
-      </c>
-      <c r="T9" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U9" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-      <c r="W9" t="str">
-        <f ca="1">'Telecaller Performance'!A13</f>
-        <v/>
-      </c>
-      <c r="X9" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X9" ca="1">IF(W9="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W9)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W9),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z9" t="str">
-        <f ca="1">'Telecaller Performance'!A13</f>
-        <v/>
-      </c>
-      <c r="AA9" t="e" cm="1">
-        <f t="array" aca="1" ref="AA9" ca="1">IF(Z9="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z9)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z9),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF9" t="str" cm="1">
-        <f t="array" ref="AF9">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF9)),"")</f>
-        <v/>
-      </c>
-      <c r="AG9" t="e" cm="1">
-        <f t="array" aca="1" ref="AG9" ca="1">IF(AF9="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF9)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF9),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="1">
-        <v>7975982783</v>
-      </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="3">
-        <v>46256.423611111109</v>
-      </c>
-      <c r="I10" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" t="s">
-        <v>15</v>
-      </c>
-      <c r="N10" t="s">
-        <v>18</v>
-      </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
-      <c r="P10" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v/>
-      </c>
-      <c r="R10" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v/>
-      </c>
-      <c r="S10" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v/>
-      </c>
-      <c r="T10" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Pass</v>
-      </c>
-      <c r="U10" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>0</v>
-      </c>
-      <c r="W10" t="str">
-        <f ca="1">'Telecaller Performance'!A14</f>
-        <v/>
-      </c>
-      <c r="X10" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X10" ca="1">IF(W10="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W10)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W10),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z10" t="str">
-        <f ca="1">'Telecaller Performance'!A14</f>
-        <v/>
-      </c>
-      <c r="AA10" t="e" cm="1">
-        <f t="array" aca="1" ref="AA10" ca="1">IF(Z10="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z10)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z10),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF10" t="str" cm="1">
-        <f t="array" ref="AF10">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF10)),"")</f>
-        <v/>
-      </c>
-      <c r="AG10" t="e" cm="1">
-        <f t="array" aca="1" ref="AG10" ca="1">IF(AF10="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF10)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF10),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="11" spans="1:36" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="1">
-        <v>8073016841</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E11" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="3">
-        <v>46256.584722222222</v>
-      </c>
-      <c r="H11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" t="s">
-        <v>29</v>
-      </c>
-      <c r="L11" t="s">
-        <v>45</v>
-      </c>
-      <c r="M11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N11" t="s">
-        <v>39</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-      <c r="P11" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Customer Location Not Captured</v>
-      </c>
-      <c r="Q11" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Anekal is the project default; customer location was not captured</v>
-      </c>
-      <c r="R11" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Contact the customer and record their actual location</v>
-      </c>
-      <c r="S11" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Medium</v>
-      </c>
-      <c r="T11" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U11" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-      <c r="W11" t="str">
-        <f ca="1">'Telecaller Performance'!A15</f>
-        <v/>
-      </c>
-      <c r="X11" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X11" ca="1">IF(W11="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W11)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W11),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z11" t="str">
-        <f ca="1">'Telecaller Performance'!A15</f>
-        <v/>
-      </c>
-      <c r="AA11" t="e" cm="1">
-        <f t="array" aca="1" ref="AA11" ca="1">IF(Z11="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z11)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z11),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF11" t="str" cm="1">
-        <f t="array" ref="AF11">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF11)),"")</f>
-        <v/>
-      </c>
-      <c r="AG11" t="e" cm="1">
-        <f t="array" aca="1" ref="AG11" ca="1">IF(AF11="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF11)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF11),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="12" spans="1:36" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="1">
-        <v>8123042533</v>
-      </c>
-      <c r="C12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="3">
-        <v>46256.465277777781</v>
-      </c>
-      <c r="H12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" t="s">
-        <v>47</v>
-      </c>
-      <c r="M12" t="s">
-        <v>38</v>
-      </c>
-      <c r="N12" t="s">
-        <v>39</v>
-      </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-      <c r="P12" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>RNR Classification Error | Customer Location Not Captured</v>
-      </c>
-      <c r="Q12" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Contact outcome should remain RNR rather than Cold
-Anekal is the project default; customer location was not captured</v>
-      </c>
-      <c r="R12" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Change lead classification to RNR and retry contact
-Contact the customer and record their actual location</v>
-      </c>
-      <c r="S12" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Critical</v>
-      </c>
-      <c r="T12" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (2 errors)</v>
-      </c>
-      <c r="U12" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>2</v>
-      </c>
-      <c r="W12" t="str">
-        <f ca="1">'Telecaller Performance'!A16</f>
-        <v/>
-      </c>
-      <c r="X12" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X12" ca="1">IF(W12="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W12)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W12),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z12" t="str">
-        <f ca="1">'Telecaller Performance'!A16</f>
-        <v/>
-      </c>
-      <c r="AA12" t="e" cm="1">
-        <f t="array" aca="1" ref="AA12" ca="1">IF(Z12="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z12)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z12),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF12" t="str" cm="1">
-        <f t="array" ref="AF12">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF12)),"")</f>
-        <v/>
-      </c>
-      <c r="AG12" t="e" cm="1">
-        <f t="array" aca="1" ref="AG12" ca="1">IF(AF12="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF12)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF12),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="1">
-        <v>8660592160</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13" s="3">
-        <v>46256.675694444442</v>
-      </c>
-      <c r="H13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J13" t="s">
-        <v>23</v>
-      </c>
-      <c r="K13" t="s">
-        <v>29</v>
-      </c>
-      <c r="L13" t="s">
-        <v>49</v>
-      </c>
-      <c r="M13" t="s">
-        <v>35</v>
-      </c>
-      <c r="N13" t="s">
-        <v>50</v>
-      </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
-      <c r="P13" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Customer Location Not Captured</v>
-      </c>
-      <c r="Q13" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Anekal is the project default; customer location was not captured</v>
-      </c>
-      <c r="R13" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Contact the customer and record their actual location</v>
-      </c>
-      <c r="S13" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Medium</v>
-      </c>
-      <c r="T13" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U13" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-      <c r="W13" t="str">
-        <f ca="1">'Telecaller Performance'!A17</f>
-        <v/>
-      </c>
-      <c r="X13" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X13" ca="1">IF(W13="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W13)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W13),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z13" t="str">
-        <f ca="1">'Telecaller Performance'!A17</f>
-        <v/>
-      </c>
-      <c r="AA13" t="e" cm="1">
-        <f t="array" aca="1" ref="AA13" ca="1">IF(Z13="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z13)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z13),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF13" t="str" cm="1">
-        <f t="array" ref="AF13">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF13)),"")</f>
-        <v/>
-      </c>
-      <c r="AG13" t="e" cm="1">
-        <f t="array" aca="1" ref="AG13" ca="1">IF(AF13="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF13)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF13),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="14" spans="1:36" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="1">
-        <v>8870745937</v>
-      </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="2">
-        <v>46254</v>
-      </c>
-      <c r="E14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="3">
-        <v>46256.430555555555</v>
-      </c>
-      <c r="H14" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J14" t="s">
-        <v>23</v>
-      </c>
-      <c r="K14" t="s">
-        <v>29</v>
-      </c>
-      <c r="L14" t="s">
-        <v>62</v>
-      </c>
-      <c r="M14" t="s">
-        <v>38</v>
-      </c>
-      <c r="N14" t="s">
-        <v>39</v>
-      </c>
-      <c r="O14">
-        <v>1</v>
-      </c>
-      <c r="P14" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Customer Location Not Captured</v>
-      </c>
-      <c r="Q14" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Anekal is the project default; customer location was not captured</v>
-      </c>
-      <c r="R14" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Contact the customer and record their actual location</v>
-      </c>
-      <c r="S14" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Medium</v>
-      </c>
-      <c r="T14" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U14" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-      <c r="W14" t="str">
-        <f ca="1">'Telecaller Performance'!A18</f>
-        <v/>
-      </c>
-      <c r="X14" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X14" ca="1">IF(W14="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W14)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W14),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z14" t="str">
-        <f ca="1">'Telecaller Performance'!A18</f>
-        <v/>
-      </c>
-      <c r="AA14" t="e" cm="1">
-        <f t="array" aca="1" ref="AA14" ca="1">IF(Z14="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z14)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z14),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF14" t="str" cm="1">
-        <f t="array" ref="AF14">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF14)),"")</f>
-        <v/>
-      </c>
-      <c r="AG14" t="e" cm="1">
-        <f t="array" aca="1" ref="AG14" ca="1">IF(AF14="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF14)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF14),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="1">
-        <v>9113651947</v>
-      </c>
-      <c r="C15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="2">
-        <v>46254</v>
-      </c>
-      <c r="E15" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="3">
-        <v>46256.470138888886</v>
-      </c>
-      <c r="I15" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J15" t="s">
-        <v>23</v>
-      </c>
-      <c r="K15" t="s">
-        <v>24</v>
-      </c>
-      <c r="L15" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15" t="s">
-        <v>15</v>
-      </c>
-      <c r="N15" t="s">
-        <v>63</v>
-      </c>
-      <c r="O15">
-        <v>1</v>
-      </c>
-      <c r="P15" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v/>
-      </c>
-      <c r="R15" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v/>
-      </c>
-      <c r="S15" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v/>
-      </c>
-      <c r="T15" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Pass</v>
-      </c>
-      <c r="U15" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>0</v>
-      </c>
-      <c r="W15" t="str">
-        <f ca="1">'Telecaller Performance'!A19</f>
-        <v/>
-      </c>
-      <c r="X15" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X15" ca="1">IF(W15="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W15)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W15),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z15" t="str">
-        <f ca="1">'Telecaller Performance'!A19</f>
-        <v/>
-      </c>
-      <c r="AA15" t="e" cm="1">
-        <f t="array" aca="1" ref="AA15" ca="1">IF(Z15="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z15)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z15),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF15" t="str" cm="1">
-        <f t="array" ref="AF15">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF15)),"")</f>
-        <v/>
-      </c>
-      <c r="AG15" t="e" cm="1">
-        <f t="array" aca="1" ref="AG15" ca="1">IF(AF15="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF15)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF15),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="16" spans="1:36" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="1">
-        <v>9380015711</v>
-      </c>
-      <c r="C16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E16" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16" s="3">
-        <v>46256.497916666667</v>
-      </c>
-      <c r="H16" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J16" t="s">
-        <v>23</v>
-      </c>
-      <c r="K16" t="s">
-        <v>24</v>
-      </c>
-      <c r="L16" t="s">
-        <v>52</v>
-      </c>
-      <c r="M16" t="s">
-        <v>38</v>
-      </c>
-      <c r="N16" t="s">
-        <v>39</v>
-      </c>
-      <c r="O16">
-        <v>1</v>
-      </c>
-      <c r="P16" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Customer Location Not Captured</v>
-      </c>
-      <c r="Q16" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Anekal is the project default; customer location was not captured</v>
-      </c>
-      <c r="R16" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Contact the customer and record their actual location</v>
-      </c>
-      <c r="S16" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Medium</v>
-      </c>
-      <c r="T16" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U16" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-      <c r="W16" t="str">
-        <f ca="1">'Telecaller Performance'!A20</f>
-        <v/>
-      </c>
-      <c r="X16" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X16" ca="1">IF(W16="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W16)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W16),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z16" t="str">
-        <f ca="1">'Telecaller Performance'!A20</f>
-        <v/>
-      </c>
-      <c r="AA16" t="e" cm="1">
-        <f t="array" aca="1" ref="AA16" ca="1">IF(Z16="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z16)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z16),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF16" t="str" cm="1">
-        <f t="array" ref="AF16">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF16)),"")</f>
-        <v/>
-      </c>
-      <c r="AG16" t="e" cm="1">
-        <f t="array" aca="1" ref="AG16" ca="1">IF(AF16="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF16)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF16),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="1">
-        <v>9425152540</v>
-      </c>
-      <c r="C17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E17" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="3">
-        <v>46256.449305555558</v>
-      </c>
-      <c r="I17" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J17" t="s">
-        <v>23</v>
-      </c>
-      <c r="K17" t="s">
-        <v>24</v>
-      </c>
-      <c r="L17" t="s">
-        <v>27</v>
-      </c>
-      <c r="M17" t="s">
-        <v>15</v>
-      </c>
-      <c r="N17" t="s">
-        <v>18</v>
-      </c>
-      <c r="O17">
-        <v>1</v>
-      </c>
-      <c r="P17" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>RNR Classification Error</v>
-      </c>
-      <c r="Q17" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Contact outcome should remain RNR rather than Cold</v>
-      </c>
-      <c r="R17" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Change lead classification to RNR and retry contact</v>
-      </c>
-      <c r="S17" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Critical</v>
-      </c>
-      <c r="T17" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U17" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-      <c r="W17" t="str">
-        <f ca="1">'Telecaller Performance'!A21</f>
-        <v/>
-      </c>
-      <c r="X17" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X17" ca="1">IF(W17="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W17)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W17),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z17" t="str">
-        <f ca="1">'Telecaller Performance'!A21</f>
-        <v/>
-      </c>
-      <c r="AA17" t="e" cm="1">
-        <f t="array" aca="1" ref="AA17" ca="1">IF(Z17="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z17)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z17),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF17" t="str" cm="1">
-        <f t="array" ref="AF17">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF17)),"")</f>
-        <v/>
-      </c>
-      <c r="AG17" t="e" cm="1">
-        <f t="array" aca="1" ref="AG17" ca="1">IF(AF17="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF17)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF17),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="18" spans="1:33" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="1">
-        <v>9482097564</v>
-      </c>
-      <c r="C18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E18" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" s="3">
-        <v>46256.445833333331</v>
-      </c>
-      <c r="H18" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J18" t="s">
-        <v>23</v>
-      </c>
-      <c r="K18" t="s">
-        <v>24</v>
-      </c>
-      <c r="L18" t="s">
-        <v>27</v>
-      </c>
-      <c r="M18" t="s">
-        <v>38</v>
-      </c>
-      <c r="N18" t="s">
-        <v>39</v>
-      </c>
-      <c r="O18">
-        <v>1</v>
-      </c>
-      <c r="P18" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Customer Location Not Captured</v>
-      </c>
-      <c r="Q18" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Anekal is the project default; customer location was not captured</v>
-      </c>
-      <c r="R18" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Contact the customer and record their actual location</v>
-      </c>
-      <c r="S18" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Medium</v>
-      </c>
-      <c r="T18" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U18" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-      <c r="W18" t="str">
-        <f ca="1">'Telecaller Performance'!A22</f>
-        <v/>
-      </c>
-      <c r="X18" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X18" ca="1">IF(W18="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W18)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W18),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z18" t="str">
-        <f ca="1">'Telecaller Performance'!A22</f>
-        <v/>
-      </c>
-      <c r="AA18" t="e" cm="1">
-        <f t="array" aca="1" ref="AA18" ca="1">IF(Z18="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z18)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z18),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF18" t="str" cm="1">
-        <f t="array" ref="AF18">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF18)),"")</f>
-        <v/>
-      </c>
-      <c r="AG18" t="e" cm="1">
-        <f t="array" aca="1" ref="AG18" ca="1">IF(AF18="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF18)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF18),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="1">
-        <v>9482159745</v>
-      </c>
-      <c r="C19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19" s="3">
-        <v>46256.452777777777</v>
-      </c>
-      <c r="I19" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J19" t="s">
-        <v>23</v>
-      </c>
-      <c r="K19" t="s">
-        <v>24</v>
-      </c>
-      <c r="L19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M19" t="s">
-        <v>15</v>
-      </c>
-      <c r="N19" t="s">
-        <v>18</v>
-      </c>
-      <c r="O19">
-        <v>1</v>
-      </c>
-      <c r="P19" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v/>
-      </c>
-      <c r="R19" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v/>
-      </c>
-      <c r="S19" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v/>
-      </c>
-      <c r="T19" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Pass</v>
-      </c>
-      <c r="U19" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>0</v>
-      </c>
-      <c r="W19" t="str">
-        <f ca="1">'Telecaller Performance'!A23</f>
-        <v/>
-      </c>
-      <c r="X19" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X19" ca="1">IF(W19="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W19)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W19),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z19" t="str">
-        <f ca="1">'Telecaller Performance'!A23</f>
-        <v/>
-      </c>
-      <c r="AA19" t="e" cm="1">
-        <f t="array" aca="1" ref="AA19" ca="1">IF(Z19="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z19)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z19),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF19" t="str" cm="1">
-        <f t="array" ref="AF19">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF19)),"")</f>
-        <v/>
-      </c>
-      <c r="AG19" t="e" cm="1">
-        <f t="array" aca="1" ref="AG19" ca="1">IF(AF19="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF19)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF19),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="20" spans="1:33" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="1">
-        <v>9482915868</v>
-      </c>
-      <c r="C20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="3">
-        <v>46256.454861111109</v>
-      </c>
-      <c r="H20" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J20" t="s">
-        <v>23</v>
-      </c>
-      <c r="K20" t="s">
-        <v>24</v>
-      </c>
-      <c r="L20" t="s">
-        <v>27</v>
-      </c>
-      <c r="M20" t="s">
-        <v>38</v>
-      </c>
-      <c r="N20" t="s">
-        <v>39</v>
-      </c>
-      <c r="O20">
-        <v>1</v>
-      </c>
-      <c r="P20" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>RNR Classification Error | Customer Location Not Captured</v>
-      </c>
-      <c r="Q20" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Contact outcome should remain RNR rather than Cold
-Anekal is the project default; customer location was not captured</v>
-      </c>
-      <c r="R20" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Change lead classification to RNR and retry contact
-Contact the customer and record their actual location</v>
-      </c>
-      <c r="S20" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Critical</v>
-      </c>
-      <c r="T20" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (2 errors)</v>
-      </c>
-      <c r="U20" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>2</v>
-      </c>
-      <c r="W20" t="str">
-        <f ca="1">'Telecaller Performance'!A24</f>
-        <v/>
-      </c>
-      <c r="X20" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X20" ca="1">IF(W20="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W20)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W20),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z20" t="str">
-        <f ca="1">'Telecaller Performance'!A24</f>
-        <v/>
-      </c>
-      <c r="AA20" t="e" cm="1">
-        <f t="array" aca="1" ref="AA20" ca="1">IF(Z20="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z20)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z20),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF20" t="str" cm="1">
-        <f t="array" ref="AF20">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF20)),"")</f>
-        <v/>
-      </c>
-      <c r="AG20" t="e" cm="1">
-        <f t="array" aca="1" ref="AG20" ca="1">IF(AF20="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF20)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF20),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="1">
-        <v>9513809427</v>
-      </c>
-      <c r="C21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E21" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="3">
-        <v>46256.493750000001</v>
-      </c>
-      <c r="I21" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J21" t="s">
-        <v>23</v>
-      </c>
-      <c r="K21" t="s">
-        <v>24</v>
-      </c>
-      <c r="L21" t="s">
-        <v>27</v>
-      </c>
-      <c r="M21" t="s">
-        <v>15</v>
-      </c>
-      <c r="N21" t="s">
-        <v>18</v>
-      </c>
-      <c r="O21">
-        <v>1</v>
-      </c>
-      <c r="P21" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v/>
-      </c>
-      <c r="R21" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v/>
-      </c>
-      <c r="S21" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v/>
-      </c>
-      <c r="T21" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Pass</v>
-      </c>
-      <c r="U21" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>0</v>
-      </c>
-      <c r="W21" t="str">
-        <f ca="1">'Telecaller Performance'!A25</f>
-        <v/>
-      </c>
-      <c r="X21" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X21" ca="1">IF(W21="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W21)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W21),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z21" t="str">
-        <f ca="1">'Telecaller Performance'!A25</f>
-        <v/>
-      </c>
-      <c r="AA21" t="e" cm="1">
-        <f t="array" aca="1" ref="AA21" ca="1">IF(Z21="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z21)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z21),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF21" t="str" cm="1">
-        <f t="array" ref="AF21">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF21)),"")</f>
-        <v/>
-      </c>
-      <c r="AG21" t="e" cm="1">
-        <f t="array" aca="1" ref="AG21" ca="1">IF(AF21="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF21)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF21),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="1">
-        <v>9538130876</v>
-      </c>
-      <c r="C22" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="2">
-        <v>46254</v>
-      </c>
-      <c r="E22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="3">
-        <v>46256.451388888891</v>
-      </c>
-      <c r="I22" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J22" t="s">
-        <v>23</v>
-      </c>
-      <c r="K22" t="s">
-        <v>24</v>
-      </c>
-      <c r="L22" t="s">
-        <v>27</v>
-      </c>
-      <c r="M22" t="s">
-        <v>15</v>
-      </c>
-      <c r="N22" t="s">
-        <v>18</v>
-      </c>
-      <c r="O22">
-        <v>1</v>
-      </c>
-      <c r="P22" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v/>
-      </c>
-      <c r="R22" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v/>
-      </c>
-      <c r="S22" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v/>
-      </c>
-      <c r="T22" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Pass</v>
-      </c>
-      <c r="U22" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>0</v>
-      </c>
-      <c r="W22" t="str">
-        <f ca="1">'Telecaller Performance'!A26</f>
-        <v/>
-      </c>
-      <c r="X22" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X22" ca="1">IF(W22="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W22)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W22),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z22" t="str">
-        <f ca="1">'Telecaller Performance'!A26</f>
-        <v/>
-      </c>
-      <c r="AA22" t="e" cm="1">
-        <f t="array" aca="1" ref="AA22" ca="1">IF(Z22="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z22)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z22),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF22" t="str" cm="1">
-        <f t="array" ref="AF22">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF22)),"")</f>
-        <v/>
-      </c>
-      <c r="AG22" t="e" cm="1">
-        <f t="array" aca="1" ref="AG22" ca="1">IF(AF22="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF22)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF22),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="23" spans="1:33" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="1">
-        <v>9663972134</v>
-      </c>
-      <c r="C23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E23" t="s">
-        <v>20</v>
-      </c>
-      <c r="F23" t="s">
-        <v>55</v>
-      </c>
-      <c r="G23" s="3">
-        <v>46256.45</v>
-      </c>
-      <c r="H23" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J23" t="s">
-        <v>23</v>
-      </c>
-      <c r="K23" t="s">
-        <v>29</v>
-      </c>
-      <c r="L23" t="s">
-        <v>56</v>
-      </c>
-      <c r="M23" t="s">
-        <v>38</v>
-      </c>
-      <c r="N23" t="s">
-        <v>39</v>
-      </c>
-      <c r="O23">
-        <v>1</v>
-      </c>
-      <c r="P23" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Customer Location Not Captured</v>
-      </c>
-      <c r="Q23" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Anekal is the project default; customer location was not captured</v>
-      </c>
-      <c r="R23" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Contact the customer and record their actual location</v>
-      </c>
-      <c r="S23" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Medium</v>
-      </c>
-      <c r="T23" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U23" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-      <c r="W23" t="str">
-        <f ca="1">'Telecaller Performance'!A27</f>
-        <v/>
-      </c>
-      <c r="X23" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X23" ca="1">IF(W23="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W23)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W23),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z23" t="str">
-        <f ca="1">'Telecaller Performance'!A27</f>
-        <v/>
-      </c>
-      <c r="AA23" t="e" cm="1">
-        <f t="array" aca="1" ref="AA23" ca="1">IF(Z23="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z23)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z23),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF23" t="str" cm="1">
-        <f t="array" ref="AF23">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF23)),"")</f>
-        <v/>
-      </c>
-      <c r="AG23" t="e" cm="1">
-        <f t="array" aca="1" ref="AG23" ca="1">IF(AF23="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF23)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF23),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="24" spans="1:33" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="1">
-        <v>9731234263</v>
-      </c>
-      <c r="C24" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E24" t="s">
-        <v>20</v>
-      </c>
-      <c r="F24" t="s">
-        <v>57</v>
-      </c>
-      <c r="G24" s="3">
-        <v>46256.490277777775</v>
-      </c>
-      <c r="H24" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J24" t="s">
-        <v>23</v>
-      </c>
-      <c r="K24" t="s">
-        <v>24</v>
-      </c>
-      <c r="L24" t="s">
-        <v>58</v>
-      </c>
-      <c r="M24" t="s">
-        <v>38</v>
-      </c>
-      <c r="N24" t="s">
-        <v>39</v>
-      </c>
-      <c r="O24">
-        <v>1</v>
-      </c>
-      <c r="P24" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Warm Status Mismatch | Customer Location Not Captured</v>
-      </c>
-      <c r="Q24" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Contact-only outcome does not support Warm status
-Anekal is the project default; customer location was not captured</v>
-      </c>
-      <c r="R24" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Validate engagement before retaining Warm status
-Contact the customer and record their actual location</v>
-      </c>
-      <c r="S24" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Medium</v>
-      </c>
-      <c r="T24" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (2 errors)</v>
-      </c>
-      <c r="U24" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>2</v>
-      </c>
-      <c r="W24" t="str">
-        <f ca="1">'Telecaller Performance'!A28</f>
-        <v/>
-      </c>
-      <c r="X24" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X24" ca="1">IF(W24="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W24)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W24),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z24" t="str">
-        <f ca="1">'Telecaller Performance'!A28</f>
-        <v/>
-      </c>
-      <c r="AA24" t="e" cm="1">
-        <f t="array" aca="1" ref="AA24" ca="1">IF(Z24="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z24)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z24),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF24" t="str" cm="1">
-        <f t="array" ref="AF24">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF24)),"")</f>
-        <v/>
-      </c>
-      <c r="AG24" t="e" cm="1">
-        <f t="array" aca="1" ref="AG24" ca="1">IF(AF24="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF24)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF24),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="25" spans="1:33" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="1">
-        <v>9742842886</v>
-      </c>
-      <c r="C25" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E25" t="s">
-        <v>20</v>
-      </c>
-      <c r="F25" t="s">
-        <v>59</v>
-      </c>
-      <c r="G25" s="3">
-        <v>46256.489583333336</v>
-      </c>
-      <c r="H25" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L25" t="s">
-        <v>60</v>
-      </c>
-      <c r="M25" t="s">
-        <v>38</v>
-      </c>
-      <c r="N25" t="s">
-        <v>39</v>
-      </c>
-      <c r="O25">
-        <v>1</v>
-      </c>
-      <c r="P25" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Warm Status Mismatch | Customer Location Not Captured</v>
-      </c>
-      <c r="Q25" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Contact-only outcome does not support Warm status
-Anekal is the project default; customer location was not captured</v>
-      </c>
-      <c r="R25" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Validate engagement before retaining Warm status
-Contact the customer and record their actual location</v>
-      </c>
-      <c r="S25" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Medium</v>
-      </c>
-      <c r="T25" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (2 errors)</v>
-      </c>
-      <c r="U25" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>2</v>
-      </c>
-      <c r="W25" t="str">
-        <f ca="1">'Telecaller Performance'!A29</f>
-        <v/>
-      </c>
-      <c r="X25" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X25" ca="1">IF(W25="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W25)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W25),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z25" t="str">
-        <f ca="1">'Telecaller Performance'!A29</f>
-        <v/>
-      </c>
-      <c r="AA25" t="e" cm="1">
-        <f t="array" aca="1" ref="AA25" ca="1">IF(Z25="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z25)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z25),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF25" t="str" cm="1">
-        <f t="array" ref="AF25">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF25)),"")</f>
-        <v/>
-      </c>
-      <c r="AG25" t="e" cm="1">
-        <f t="array" aca="1" ref="AG25" ca="1">IF(AF25="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF25)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF25),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="1">
-        <v>9844043359</v>
-      </c>
-      <c r="C26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="2">
-        <v>46254</v>
-      </c>
-      <c r="E26" t="s">
-        <v>20</v>
-      </c>
-      <c r="F26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G26" s="3">
-        <v>46256.427083333336</v>
-      </c>
-      <c r="I26" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J26" t="s">
-        <v>23</v>
-      </c>
-      <c r="K26" t="s">
-        <v>24</v>
-      </c>
-      <c r="L26" t="s">
-        <v>65</v>
-      </c>
-      <c r="M26" t="s">
-        <v>15</v>
-      </c>
-      <c r="N26" t="s">
-        <v>18</v>
-      </c>
-      <c r="O26">
-        <v>1</v>
-      </c>
-      <c r="P26" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v/>
-      </c>
-      <c r="R26" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v/>
-      </c>
-      <c r="S26" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v/>
-      </c>
-      <c r="T26" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Pass</v>
-      </c>
-      <c r="U26" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>0</v>
-      </c>
-      <c r="W26" t="str">
-        <f ca="1">'Telecaller Performance'!A30</f>
-        <v/>
-      </c>
-      <c r="X26" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X26" ca="1">IF(W26="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W26)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W26),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z26" t="str">
-        <f ca="1">'Telecaller Performance'!A30</f>
-        <v/>
-      </c>
-      <c r="AA26" t="e" cm="1">
-        <f t="array" aca="1" ref="AA26" ca="1">IF(Z26="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z26)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z26),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF26" t="str" cm="1">
-        <f t="array" ref="AF26">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF26)),"")</f>
-        <v/>
-      </c>
-      <c r="AG26" t="e" cm="1">
-        <f t="array" aca="1" ref="AG26" ca="1">IF(AF26="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF26)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF26),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="27" spans="1:33" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="1">
-        <v>9866183030</v>
-      </c>
-      <c r="C27" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E27" t="s">
-        <v>20</v>
-      </c>
-      <c r="F27" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="3">
-        <v>46256.460416666669</v>
-      </c>
-      <c r="H27" t="s">
-        <v>22</v>
-      </c>
-      <c r="I27" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J27" t="s">
-        <v>23</v>
-      </c>
-      <c r="K27" t="s">
-        <v>24</v>
-      </c>
-      <c r="L27" t="s">
-        <v>26</v>
-      </c>
-      <c r="M27" t="s">
-        <v>38</v>
-      </c>
-      <c r="N27" t="s">
-        <v>39</v>
-      </c>
-      <c r="O27">
-        <v>1</v>
-      </c>
-      <c r="P27" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Customer Location Not Captured</v>
-      </c>
-      <c r="Q27" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Anekal is the project default; customer location was not captured</v>
-      </c>
-      <c r="R27" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Contact the customer and record their actual location</v>
-      </c>
-      <c r="S27" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Medium</v>
-      </c>
-      <c r="T27" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U27" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-      <c r="W27" t="str">
-        <f ca="1">'Telecaller Performance'!A31</f>
-        <v/>
-      </c>
-      <c r="X27" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X27" ca="1">IF(W27="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W27)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W27),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z27" t="str">
-        <f ca="1">'Telecaller Performance'!A31</f>
-        <v/>
-      </c>
-      <c r="AA27" t="e" cm="1">
-        <f t="array" aca="1" ref="AA27" ca="1">IF(Z27="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z27)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z27),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF27" t="str" cm="1">
-        <f t="array" ref="AF27">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF27)),"")</f>
-        <v/>
-      </c>
-      <c r="AG27" t="e" cm="1">
-        <f t="array" aca="1" ref="AG27" ca="1">IF(AF27="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF27)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF27),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="1">
-        <v>9886445543</v>
-      </c>
-      <c r="C28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="2">
-        <v>46254</v>
-      </c>
-      <c r="E28" t="s">
-        <v>20</v>
-      </c>
-      <c r="F28" t="s">
-        <v>66</v>
-      </c>
-      <c r="G28" s="3">
-        <v>46256.538194444445</v>
-      </c>
-      <c r="I28" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J28" t="s">
-        <v>23</v>
-      </c>
-      <c r="K28" t="s">
-        <v>29</v>
-      </c>
-      <c r="L28" t="s">
-        <v>67</v>
-      </c>
-      <c r="M28" t="s">
-        <v>15</v>
-      </c>
-      <c r="N28" t="s">
-        <v>18</v>
-      </c>
-      <c r="O28">
-        <v>1</v>
-      </c>
-      <c r="P28" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v/>
-      </c>
-      <c r="R28" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v/>
-      </c>
-      <c r="S28" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v/>
-      </c>
-      <c r="T28" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Pass</v>
-      </c>
-      <c r="U28" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>0</v>
-      </c>
-      <c r="W28" t="str">
-        <f ca="1">'Telecaller Performance'!A32</f>
-        <v/>
-      </c>
-      <c r="X28" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X28" ca="1">IF(W28="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W28)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W28),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z28" t="str">
-        <f ca="1">'Telecaller Performance'!A32</f>
-        <v/>
-      </c>
-      <c r="AA28" t="e" cm="1">
-        <f t="array" aca="1" ref="AA28" ca="1">IF(Z28="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z28)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z28),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF28" t="str" cm="1">
-        <f t="array" ref="AF28">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF28)),"")</f>
-        <v/>
-      </c>
-      <c r="AG28" t="e" cm="1">
-        <f t="array" aca="1" ref="AG28" ca="1">IF(AF28="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF28)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF28),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="29" spans="1:33" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="1">
-        <v>9980197119</v>
-      </c>
-      <c r="C29" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="2">
-        <v>46254</v>
-      </c>
-      <c r="E29" t="s">
-        <v>20</v>
-      </c>
-      <c r="F29" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="3">
-        <v>46256.442361111112</v>
-      </c>
-      <c r="H29" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J29" t="s">
-        <v>23</v>
-      </c>
-      <c r="K29" t="s">
-        <v>24</v>
-      </c>
-      <c r="L29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M29" t="s">
-        <v>38</v>
-      </c>
-      <c r="N29" t="s">
-        <v>39</v>
-      </c>
-      <c r="O29">
-        <v>1</v>
-      </c>
-      <c r="P29" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Customer Location Not Captured</v>
-      </c>
-      <c r="Q29" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Anekal is the project default; customer location was not captured</v>
-      </c>
-      <c r="R29" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Contact the customer and record their actual location</v>
-      </c>
-      <c r="S29" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Medium</v>
-      </c>
-      <c r="T29" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U29" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-      <c r="W29" t="str">
-        <f ca="1">'Telecaller Performance'!A33</f>
-        <v/>
-      </c>
-      <c r="X29" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X29" ca="1">IF(W29="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W29)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W29),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z29" t="str">
-        <f ca="1">'Telecaller Performance'!A33</f>
-        <v/>
-      </c>
-      <c r="AA29" t="e" cm="1">
-        <f t="array" aca="1" ref="AA29" ca="1">IF(Z29="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z29)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z29),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF29" t="str" cm="1">
-        <f t="array" ref="AF29">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF29)),"")</f>
-        <v/>
-      </c>
-      <c r="AG29" t="e" cm="1">
-        <f t="array" aca="1" ref="AG29" ca="1">IF(AF29="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF29)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF29),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1">
-        <v>9986227911</v>
-      </c>
-      <c r="C30" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="2">
-        <v>46254</v>
-      </c>
-      <c r="E30" t="s">
-        <v>20</v>
-      </c>
-      <c r="F30" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="3">
-        <v>46256.450694444444</v>
-      </c>
-      <c r="I30" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K30" t="s">
-        <v>29</v>
-      </c>
-      <c r="L30" t="s">
-        <v>27</v>
-      </c>
-      <c r="M30" t="s">
-        <v>15</v>
-      </c>
-      <c r="N30" t="s">
-        <v>18</v>
-      </c>
-      <c r="O30">
-        <v>1</v>
-      </c>
-      <c r="P30" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v/>
-      </c>
-      <c r="R30" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v/>
-      </c>
-      <c r="S30" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v/>
-      </c>
-      <c r="T30" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Pass</v>
-      </c>
-      <c r="U30" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>0</v>
-      </c>
-      <c r="W30" t="str">
-        <f ca="1">'Telecaller Performance'!A34</f>
-        <v/>
-      </c>
-      <c r="X30" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X30" ca="1">IF(W30="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W30)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W30),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z30" t="str">
-        <f ca="1">'Telecaller Performance'!A34</f>
-        <v/>
-      </c>
-      <c r="AA30" t="e" cm="1">
-        <f t="array" aca="1" ref="AA30" ca="1">IF(Z30="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z30)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z30),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF30" t="str" cm="1">
-        <f t="array" ref="AF30">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF30)),"")</f>
-        <v/>
-      </c>
-      <c r="AG30" t="e" cm="1">
-        <f t="array" aca="1" ref="AG30" ca="1">IF(AF30="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF30)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF30),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>68</v>
-      </c>
-      <c r="B31" s="1">
-        <v>8792113565</v>
-      </c>
-      <c r="C31" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="2">
-        <v>46253</v>
-      </c>
-      <c r="E31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F31" t="s">
-        <v>69</v>
-      </c>
-      <c r="G31" s="3">
-        <v>46275.465277777781</v>
-      </c>
-      <c r="I31" s="4">
-        <v>-20</v>
-      </c>
-      <c r="J31" t="s">
-        <v>23</v>
-      </c>
-      <c r="K31" t="s">
-        <v>29</v>
-      </c>
-      <c r="L31" t="s">
-        <v>70</v>
-      </c>
-      <c r="M31" t="s">
-        <v>35</v>
-      </c>
-      <c r="N31" t="s">
-        <v>36</v>
-      </c>
-      <c r="O31">
-        <v>1</v>
-      </c>
-      <c r="P31" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v/>
-      </c>
-      <c r="R31" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v/>
-      </c>
-      <c r="S31" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v/>
-      </c>
-      <c r="T31" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Pass</v>
-      </c>
-      <c r="U31" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>0</v>
-      </c>
-      <c r="W31" t="str">
-        <f ca="1">'Telecaller Performance'!A35</f>
-        <v/>
-      </c>
-      <c r="X31" s="8" t="e" cm="1">
-        <f t="array" aca="1" ref="X31" ca="1">IF(W31="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W31)),IF(_xlpm.z=0,NA(),MAX(0,1-SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=W31),RawData[Error Flag])/_xlpm.z))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z31" t="str">
-        <f ca="1">'Telecaller Performance'!A35</f>
-        <v/>
-      </c>
-      <c r="AA31" t="e" cm="1">
-        <f t="array" aca="1" ref="AA31" ca="1">IF(Z31="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z31)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Telecaller Name]=Z31),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF31" t="str" cm="1">
-        <f t="array" ref="AF31">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],RawData[Project Name]&lt;&gt;""))),ROWS(AF$2:AF31)),"")</f>
-        <v/>
-      </c>
-      <c r="AG31" t="e" cm="1">
-        <f t="array" aca="1" ref="AG31" ca="1">IF(AF31="",NA(),_xlfn.LET(_xlpm.v,SUBTOTAL(103,OFFSET(RawData[Mobile],ROW(RawData[Mobile])-MIN(ROW(RawData[Mobile])),0,1)),_xlpm.z,SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF31)),IF(_xlpm.z=0,NA(),SUMPRODUCT(_xlpm.v,--(RawData[Project Name]=AF31),RawData[Error Flag]))))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="32" spans="1:33" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>68</v>
-      </c>
-      <c r="B32" s="1">
-        <v>9113032590</v>
-      </c>
-      <c r="C32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32" s="2">
-        <v>46254</v>
-      </c>
-      <c r="E32" t="s">
-        <v>20</v>
-      </c>
-      <c r="F32" t="s">
-        <v>71</v>
-      </c>
-      <c r="G32" s="3">
-        <v>46255.624305555553</v>
-      </c>
-      <c r="I32" s="4">
-        <v>0</v>
-      </c>
-      <c r="J32" t="s">
-        <v>23</v>
-      </c>
-      <c r="K32" t="s">
-        <v>29</v>
-      </c>
-      <c r="L32" t="s">
-        <v>72</v>
-      </c>
-      <c r="M32" t="s">
-        <v>35</v>
-      </c>
-      <c r="N32" t="s">
-        <v>73</v>
-      </c>
-      <c r="O32">
-        <v>1</v>
-      </c>
-      <c r="P32" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Follow-up Error</v>
-      </c>
-      <c r="Q32" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Follow-up date/time has passed for an active lead</v>
-      </c>
-      <c r="R32" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Contact immediately and set the next follow-up</v>
-      </c>
-      <c r="S32" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Critical</v>
-      </c>
-      <c r="T32" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U32" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" s="1">
-        <v>8451989990</v>
-      </c>
-      <c r="C33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D33" s="2">
-        <v>46254</v>
-      </c>
-      <c r="E33" t="s">
-        <v>46</v>
-      </c>
-      <c r="F33" t="s">
-        <v>79</v>
-      </c>
-      <c r="G33" s="3">
-        <v>46260.651388888888</v>
-      </c>
-      <c r="I33" s="4">
-        <v>-5</v>
-      </c>
-      <c r="J33" t="s">
-        <v>23</v>
-      </c>
-      <c r="K33" t="s">
-        <v>80</v>
-      </c>
-      <c r="L33" t="s">
-        <v>81</v>
-      </c>
-      <c r="M33" t="s">
-        <v>15</v>
-      </c>
-      <c r="N33" t="s">
-        <v>18</v>
-      </c>
-      <c r="O33">
-        <v>1</v>
-      </c>
-      <c r="P33" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Wrong Lead Status</v>
-      </c>
-      <c r="Q33" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Engagement intent conflicts with Cold/Lost status</v>
-      </c>
-      <c r="R33" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Reclassify lead and schedule a documented follow-up</v>
-      </c>
-      <c r="S33" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Critical</v>
-      </c>
-      <c r="T33" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U33" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>74</v>
-      </c>
-      <c r="B34" s="1">
-        <v>9342563551</v>
-      </c>
-      <c r="C34" t="s">
-        <v>86</v>
-      </c>
-      <c r="D34" s="2">
-        <v>46254</v>
-      </c>
-      <c r="E34" t="s">
-        <v>46</v>
-      </c>
-      <c r="F34" t="s">
-        <v>87</v>
-      </c>
-      <c r="G34" s="3">
-        <v>46256.449305555558</v>
-      </c>
-      <c r="I34" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J34" t="s">
-        <v>23</v>
-      </c>
-      <c r="M34" t="s">
-        <v>15</v>
-      </c>
-      <c r="N34" t="s">
-        <v>18</v>
-      </c>
-      <c r="O34">
-        <v>1</v>
-      </c>
-      <c r="P34" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v/>
-      </c>
-      <c r="R34" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v/>
-      </c>
-      <c r="S34" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v/>
-      </c>
-      <c r="T34" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Pass</v>
-      </c>
-      <c r="U34" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>74</v>
-      </c>
-      <c r="B35" s="1">
-        <v>9538130876</v>
-      </c>
-      <c r="C35" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35" s="2">
-        <v>46254</v>
-      </c>
-      <c r="E35" t="s">
-        <v>46</v>
-      </c>
-      <c r="F35" t="s">
-        <v>82</v>
-      </c>
-      <c r="G35" s="3">
-        <v>46256.581250000003</v>
-      </c>
-      <c r="I35" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J35" t="s">
-        <v>23</v>
-      </c>
-      <c r="K35" t="s">
-        <v>29</v>
-      </c>
-      <c r="L35" t="s">
-        <v>83</v>
-      </c>
-      <c r="M35" t="s">
-        <v>15</v>
-      </c>
-      <c r="N35" t="s">
-        <v>18</v>
-      </c>
-      <c r="O35">
-        <v>1</v>
-      </c>
-      <c r="P35" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Wrong Lead Status</v>
-      </c>
-      <c r="Q35" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Engagement intent conflicts with Cold/Lost status</v>
-      </c>
-      <c r="R35" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Reclassify lead and schedule a documented follow-up</v>
-      </c>
-      <c r="S35" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Critical</v>
-      </c>
-      <c r="T35" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U35" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>74</v>
-      </c>
-      <c r="B36" s="1">
-        <v>9620403822</v>
-      </c>
-      <c r="C36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36" s="2">
-        <v>46254</v>
-      </c>
-      <c r="E36" t="s">
-        <v>43</v>
-      </c>
-      <c r="F36" t="s">
-        <v>75</v>
-      </c>
-      <c r="G36" s="3">
-        <v>46256.415972222225</v>
-      </c>
-      <c r="H36" t="s">
-        <v>76</v>
-      </c>
-      <c r="I36" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J36" t="s">
-        <v>23</v>
-      </c>
-      <c r="K36" t="s">
-        <v>29</v>
-      </c>
-      <c r="L36" t="s">
-        <v>77</v>
-      </c>
-      <c r="M36" t="s">
-        <v>35</v>
-      </c>
-      <c r="N36" t="s">
-        <v>36</v>
-      </c>
-      <c r="O36">
-        <v>1</v>
-      </c>
-      <c r="P36" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v/>
-      </c>
-      <c r="R36" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v/>
-      </c>
-      <c r="S36" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v/>
-      </c>
-      <c r="T36" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Pass</v>
-      </c>
-      <c r="U36" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>74</v>
-      </c>
-      <c r="B37" s="1">
-        <v>9986227911</v>
-      </c>
-      <c r="C37" t="s">
-        <v>78</v>
-      </c>
-      <c r="D37" s="2">
-        <v>46254</v>
-      </c>
-      <c r="E37" t="s">
-        <v>46</v>
-      </c>
-      <c r="F37" t="s">
-        <v>84</v>
-      </c>
-      <c r="G37" s="3">
-        <v>46256.572916666664</v>
-      </c>
-      <c r="I37" s="4">
-        <v>-1</v>
-      </c>
-      <c r="J37" t="s">
-        <v>23</v>
-      </c>
-      <c r="K37" t="s">
-        <v>29</v>
-      </c>
-      <c r="L37" t="s">
-        <v>85</v>
-      </c>
-      <c r="M37" t="s">
-        <v>15</v>
-      </c>
-      <c r="N37" t="s">
-        <v>18</v>
-      </c>
-      <c r="O37">
-        <v>1</v>
-      </c>
-      <c r="P37" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Wrong Lead Status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"RNR Classification Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Warm Status Mismatch",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"CRM Status Mismatch",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up Error",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Customer Location Not Captured","")))</f>
-        <v>Wrong Lead Status</v>
-      </c>
-      <c r="Q37" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Engagement intent conflicts with Cold/Lost status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Contact outcome should remain RNR rather than Cold",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Contact-only outcome does not support Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Requirements were captured while CRM status remains RNR",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Follow-up date/time has passed for an active lead",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Anekal is the project default; customer location was not captured","")))</f>
-        <v>Engagement intent conflicts with Cold/Lost status</v>
-      </c>
-      <c r="R37" s="6" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))),"Reclassify lead and schedule a documented follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")),"Change lead classification to RNR and retry contact",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")),"Validate engagement before retaining Warm status",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))),"Update CRM status to reflect the collected requirement",""),IF(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")),"Contact immediately and set the next follow-up",""),IF(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]]))))),"Contact the customer and record their actual location","")))</f>
-        <v>Reclassify lead and schedule a documented follow-up</v>
-      </c>
-      <c r="S37" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"",IF(OR(ISNUMBER(SEARCH("Wrong Lead Status",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("RNR Classification Error",RawData[[#This Row],[Error Type]])),ISNUMBER(SEARCH("Follow-up Error",RawData[[#This Row],[Error Type]]))),"Critical","Medium"))</f>
-        <v>Critical</v>
-      </c>
-      <c r="T37" t="str">
-        <f ca="1">IF(RawData[[#This Row],[Error Flag]]=0,"Pass","Action Required ("&amp;RawData[[#This Row],[Error Flag]]&amp;IF(RawData[[#This Row],[Error Flag]]=1," error)"," errors)"))</f>
-        <v>Action Required (1 error)</v>
-      </c>
-      <c r="U37" s="4">
-        <f ca="1">IF(RawData[[#This Row],[Mobile]]="",0,--(AND(OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="lost"),OR(ISNUMBER(SEARCH("visit",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("brochure",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("pricing",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("price",LOWER(TRIM(RawData[[#This Row],[Comments]])))),ISNUMBER(SEARCH("budget",LOWER(TRIM(RawData[[#This Row],[Comments]])))))))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="cold",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="rnr",LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="out of network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="outoff network",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm",OR(LOWER(TRIM(RawData[[#This Row],[Comments]]))="busy",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voice mail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="voicemail",LOWER(TRIM(RawData[[#This Row],[Comments]]))="call back later")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Status]]))="rnr",OR(ISNUMBER(SEARCH("requirement",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("budget",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("location",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("purpose",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("dimension",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))),ISNUMBER(SEARCH("sqft",LOWER(RawData[[#This Row],[Comments]]&amp;" "&amp;RawData[[#This Row],[Customer Requirement]]))))))+--(AND(ISNUMBER(RawData[[#This Row],[Next Followup Date]]),RawData[[#This Row],[Next Followup Date]]&lt;NOW(),OR(LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="hot",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="prospect",LOWER(TRIM(RawData[[#This Row],[Lead Status]]))="warm")))+--(AND(LOWER(TRIM(RawData[[#This Row],[Location]]))="anekal",OR(ISNUMBER(SEARCH("ernika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("enrika",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH("exotica",LOWER(RawData[[#This Row],[Project Name]]))),ISNUMBER(SEARCH(" eka",LOWER(RawData[[#This Row],[Project Name]])))))))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="F38"/>
-      <c r="M38"/>
-      <c r="N38"/>
-      <c r="O38"/>
-      <c r="P38"/>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="F39"/>
-      <c r="M39"/>
-      <c r="N39"/>
-      <c r="O39"/>
-      <c r="P39"/>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="F40"/>
-      <c r="M40"/>
-      <c r="N40"/>
-      <c r="O40"/>
-      <c r="P40"/>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="F41"/>
-      <c r="M41"/>
-      <c r="N41"/>
-      <c r="O41"/>
-      <c r="P41"/>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="F42"/>
-      <c r="M42"/>
-      <c r="N42"/>
-      <c r="O42"/>
-      <c r="P42"/>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="F43"/>
-      <c r="M43"/>
-      <c r="N43"/>
-      <c r="O43"/>
-      <c r="P43"/>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="F44"/>
-      <c r="M44"/>
-      <c r="N44"/>
-      <c r="O44"/>
-      <c r="P44"/>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="F45"/>
-      <c r="M45"/>
-      <c r="N45"/>
-      <c r="O45"/>
-      <c r="P45"/>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="F46"/>
-      <c r="M46"/>
-      <c r="N46"/>
-      <c r="O46"/>
-      <c r="P46"/>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="F47"/>
-      <c r="M47"/>
-      <c r="N47"/>
-      <c r="O47"/>
-      <c r="P47"/>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="F48"/>
-      <c r="M48"/>
-      <c r="N48"/>
-      <c r="O48"/>
-      <c r="P48"/>
-    </row>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="62" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="63" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="64" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="65" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="66" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="67" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="68" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="69" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="70" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="71" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="72" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="73" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="74" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="75" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="76" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="77" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="78" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="79" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="80" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="82" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="83" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="84" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="85" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="86" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="87" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="88" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="89" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="90" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="91" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="92" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="93" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="94" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="95" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="96" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="97" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="98" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="99" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="100" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="101" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="102" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="103" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="104" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="105" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="106" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="107" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="108" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="109" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="110" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="111" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="112" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="113" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="114" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="115" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="116" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="117" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="118" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="119" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="120" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="121" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="122" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="123" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="124" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="125" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="126" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="127" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="128" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="129" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="130" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="131" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="132" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="133" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="134" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="135" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="136" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="137" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="138" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="139" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="140" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="141" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="142" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="143" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="144" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="145" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="146" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="147" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="148" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="149" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="150" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="151" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="152" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="153" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="154" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="155" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="156" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="157" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="158" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="159" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="160" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="161" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="162" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="163" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="164" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="165" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="166" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="167" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="168" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="169" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="170" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="171" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="172" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="173" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="174" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="175" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="176" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="177" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="178" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="179" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="180" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="181" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="182" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="183" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="184" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="185" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="186" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="187" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="188" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="189" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="190" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="191" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="192" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="193" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="194" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="195" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="196" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="197" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="198" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="199" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="200" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="V1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -19759,6 +16069,2168 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N51"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Telecaller</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Telecaller</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Errors</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Error Type</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Errors</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),1),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B2" s="9">
+        <f>IF(A2="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A2,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A2,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D2" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),1),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E2">
+        <f>IF(D2="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D2,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G2" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),1),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>IF(G2="","",COUNTIFS(RawData[Error Type],G2,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J2" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),1),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>IF(J2="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J2,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M2" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),1),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>IF(M2="","",COUNTIFS(RawData[Severity],M2,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),2),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B3" s="9">
+        <f>IF(A3="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A3,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A3,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D3" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),2),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>IF(D3="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D3,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G3" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),2),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H3">
+        <f>IF(G3="","",COUNTIFS(RawData[Error Type],G3,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J3" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),2),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K3">
+        <f>IF(J3="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J3,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M3" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),2),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N3">
+        <f>IF(M3="","",COUNTIFS(RawData[Severity],M3,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),3),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B4" s="9">
+        <f>IF(A4="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A4,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A4,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D4" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),3),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>IF(D4="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D4,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G4" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),3),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H4">
+        <f>IF(G4="","",COUNTIFS(RawData[Error Type],G4,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J4" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),3),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K4">
+        <f>IF(J4="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J4,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M4" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),3),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N4">
+        <f>IF(M4="","",COUNTIFS(RawData[Severity],M4,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),4),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B5" s="9">
+        <f>IF(A5="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A5,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A5,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D5" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),4),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>IF(D5="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D5,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G5" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),4),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>IF(G5="","",COUNTIFS(RawData[Error Type],G5,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J5" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),4),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K5">
+        <f>IF(J5="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J5,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M5" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),4),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N5">
+        <f>IF(M5="","",COUNTIFS(RawData[Severity],M5,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),5),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B6" s="9">
+        <f>IF(A6="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A6,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A6,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D6" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),5),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>IF(D6="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D6,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G6" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),5),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>IF(G6="","",COUNTIFS(RawData[Error Type],G6,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J6" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),5),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K6">
+        <f>IF(J6="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J6,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M6" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),5),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N6">
+        <f>IF(M6="","",COUNTIFS(RawData[Severity],M6,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),6),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B7" s="9">
+        <f>IF(A7="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A7,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A7,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D7" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),6),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>IF(D7="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D7,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G7" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),6),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>IF(G7="","",COUNTIFS(RawData[Error Type],G7,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J7" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),6),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K7">
+        <f>IF(J7="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J7,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M7" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),6),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N7">
+        <f>IF(M7="","",COUNTIFS(RawData[Severity],M7,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),7),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B8" s="9">
+        <f>IF(A8="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A8,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A8,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D8" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),7),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>IF(D8="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D8,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G8" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),7),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IF(G8="","",COUNTIFS(RawData[Error Type],G8,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J8" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),7),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>IF(J8="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J8,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M8" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),7),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N8">
+        <f>IF(M8="","",COUNTIFS(RawData[Severity],M8,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),8),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B9" s="9">
+        <f>IF(A9="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A9,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A9,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D9" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),8),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>IF(D9="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D9,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G9" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),8),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>IF(G9="","",COUNTIFS(RawData[Error Type],G9,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J9" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),8),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K9">
+        <f>IF(J9="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J9,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M9" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),8),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N9">
+        <f>IF(M9="","",COUNTIFS(RawData[Severity],M9,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),9),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B10" s="9">
+        <f>IF(A10="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A10,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A10,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D10" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),9),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>IF(D10="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D10,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G10" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),9),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>IF(G10="","",COUNTIFS(RawData[Error Type],G10,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J10" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),9),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K10">
+        <f>IF(J10="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J10,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M10" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),9),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N10">
+        <f>IF(M10="","",COUNTIFS(RawData[Severity],M10,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),10),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B11" s="9">
+        <f>IF(A11="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A11,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A11,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D11" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),10),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>IF(D11="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D11,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G11" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),10),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>IF(G11="","",COUNTIFS(RawData[Error Type],G11,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J11" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),10),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K11">
+        <f>IF(J11="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J11,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M11" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),10),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N11">
+        <f>IF(M11="","",COUNTIFS(RawData[Severity],M11,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),11),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B12" s="9">
+        <f>IF(A12="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A12,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A12,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D12" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),11),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>IF(D12="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D12,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G12" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),11),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>IF(G12="","",COUNTIFS(RawData[Error Type],G12,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J12" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),11),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K12">
+        <f>IF(J12="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J12,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M12" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),11),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N12">
+        <f>IF(M12="","",COUNTIFS(RawData[Severity],M12,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),12),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B13" s="9">
+        <f>IF(A13="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A13,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A13,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D13" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),12),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>IF(D13="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D13,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G13" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),12),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>IF(G13="","",COUNTIFS(RawData[Error Type],G13,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J13" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),12),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K13">
+        <f>IF(J13="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J13,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M13" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),12),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N13">
+        <f>IF(M13="","",COUNTIFS(RawData[Severity],M13,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),13),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B14" s="9">
+        <f>IF(A14="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A14,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A14,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D14" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),13),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>IF(D14="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D14,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G14" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),13),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>IF(G14="","",COUNTIFS(RawData[Error Type],G14,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J14" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),13),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K14">
+        <f>IF(J14="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J14,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M14" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),13),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N14">
+        <f>IF(M14="","",COUNTIFS(RawData[Severity],M14,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),14),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B15" s="9">
+        <f>IF(A15="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A15,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A15,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D15" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),14),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>IF(D15="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D15,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G15" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),14),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>IF(G15="","",COUNTIFS(RawData[Error Type],G15,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J15" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),14),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K15">
+        <f>IF(J15="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J15,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M15" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),14),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N15">
+        <f>IF(M15="","",COUNTIFS(RawData[Severity],M15,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),15),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B16" s="9">
+        <f>IF(A16="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A16,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A16,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D16" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),15),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E16">
+        <f>IF(D16="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D16,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G16" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),15),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H16">
+        <f>IF(G16="","",COUNTIFS(RawData[Error Type],G16,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J16" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),15),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K16">
+        <f>IF(J16="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J16,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M16" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),15),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N16">
+        <f>IF(M16="","",COUNTIFS(RawData[Severity],M16,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),16),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B17" s="9">
+        <f>IF(A17="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A17,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A17,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D17" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),16),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E17">
+        <f>IF(D17="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D17,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G17" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),16),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H17">
+        <f>IF(G17="","",COUNTIFS(RawData[Error Type],G17,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J17" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),16),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K17">
+        <f>IF(J17="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J17,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M17" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),16),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N17">
+        <f>IF(M17="","",COUNTIFS(RawData[Severity],M17,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),17),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B18" s="9">
+        <f>IF(A18="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A18,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A18,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D18" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),17),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E18">
+        <f>IF(D18="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D18,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G18" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),17),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H18">
+        <f>IF(G18="","",COUNTIFS(RawData[Error Type],G18,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J18" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),17),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K18">
+        <f>IF(J18="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J18,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M18" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),17),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N18">
+        <f>IF(M18="","",COUNTIFS(RawData[Severity],M18,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),18),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B19" s="9">
+        <f>IF(A19="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A19,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A19,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D19" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),18),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E19">
+        <f>IF(D19="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D19,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G19" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),18),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H19">
+        <f>IF(G19="","",COUNTIFS(RawData[Error Type],G19,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J19" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),18),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K19">
+        <f>IF(J19="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J19,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M19" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),18),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N19">
+        <f>IF(M19="","",COUNTIFS(RawData[Severity],M19,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),19),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B20" s="9">
+        <f>IF(A20="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A20,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A20,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D20" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),19),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E20">
+        <f>IF(D20="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D20,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G20" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),19),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H20">
+        <f>IF(G20="","",COUNTIFS(RawData[Error Type],G20,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J20" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),19),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K20">
+        <f>IF(J20="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J20,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M20" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),19),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N20">
+        <f>IF(M20="","",COUNTIFS(RawData[Severity],M20,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),20),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B21" s="9">
+        <f>IF(A21="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A21,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A21,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D21" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),20),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E21">
+        <f>IF(D21="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D21,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G21" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),20),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H21">
+        <f>IF(G21="","",COUNTIFS(RawData[Error Type],G21,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J21" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),20),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K21">
+        <f>IF(J21="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J21,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M21" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),20),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N21">
+        <f>IF(M21="","",COUNTIFS(RawData[Severity],M21,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),21),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B22" s="9">
+        <f>IF(A22="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A22,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A22,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D22" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),21),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E22">
+        <f>IF(D22="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D22,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G22" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),21),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H22">
+        <f>IF(G22="","",COUNTIFS(RawData[Error Type],G22,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J22" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),21),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K22">
+        <f>IF(J22="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J22,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M22" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),21),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N22">
+        <f>IF(M22="","",COUNTIFS(RawData[Severity],M22,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),22),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B23" s="9">
+        <f>IF(A23="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A23,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A23,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D23" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),22),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E23">
+        <f>IF(D23="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D23,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G23" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),22),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H23">
+        <f>IF(G23="","",COUNTIFS(RawData[Error Type],G23,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J23" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),22),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K23">
+        <f>IF(J23="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J23,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M23" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),22),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N23">
+        <f>IF(M23="","",COUNTIFS(RawData[Severity],M23,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),23),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B24" s="9">
+        <f>IF(A24="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A24,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A24,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D24" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),23),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E24">
+        <f>IF(D24="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D24,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G24" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),23),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H24">
+        <f>IF(G24="","",COUNTIFS(RawData[Error Type],G24,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J24" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),23),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K24">
+        <f>IF(J24="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J24,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M24" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),23),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N24">
+        <f>IF(M24="","",COUNTIFS(RawData[Severity],M24,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),24),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B25" s="9">
+        <f>IF(A25="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A25,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A25,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D25" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),24),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E25">
+        <f>IF(D25="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D25,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G25" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),24),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H25">
+        <f>IF(G25="","",COUNTIFS(RawData[Error Type],G25,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J25" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),24),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K25">
+        <f>IF(J25="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J25,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M25" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),24),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N25">
+        <f>IF(M25="","",COUNTIFS(RawData[Severity],M25,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),25),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B26" s="9">
+        <f>IF(A26="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A26,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A26,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D26" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),25),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E26">
+        <f>IF(D26="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D26,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G26" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),25),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H26">
+        <f>IF(G26="","",COUNTIFS(RawData[Error Type],G26,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J26" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),25),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K26">
+        <f>IF(J26="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J26,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M26" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),25),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N26">
+        <f>IF(M26="","",COUNTIFS(RawData[Severity],M26,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),26),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B27" s="9">
+        <f>IF(A27="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A27,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A27,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D27" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),26),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E27">
+        <f>IF(D27="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D27,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G27" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),26),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H27">
+        <f>IF(G27="","",COUNTIFS(RawData[Error Type],G27,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J27" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),26),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K27">
+        <f>IF(J27="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J27,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M27" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),26),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N27">
+        <f>IF(M27="","",COUNTIFS(RawData[Severity],M27,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),27),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B28" s="9">
+        <f>IF(A28="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A28,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A28,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D28" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),27),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E28">
+        <f>IF(D28="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D28,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G28" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),27),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H28">
+        <f>IF(G28="","",COUNTIFS(RawData[Error Type],G28,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J28" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),27),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K28">
+        <f>IF(J28="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J28,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M28" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),27),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N28">
+        <f>IF(M28="","",COUNTIFS(RawData[Severity],M28,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),28),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B29" s="9">
+        <f>IF(A29="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A29,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A29,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D29" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),28),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E29">
+        <f>IF(D29="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D29,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G29" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),28),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H29">
+        <f>IF(G29="","",COUNTIFS(RawData[Error Type],G29,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J29" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),28),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K29">
+        <f>IF(J29="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J29,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M29" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),28),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N29">
+        <f>IF(M29="","",COUNTIFS(RawData[Severity],M29,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),29),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B30" s="9">
+        <f>IF(A30="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A30,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A30,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D30" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),29),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E30">
+        <f>IF(D30="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D30,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G30" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),29),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H30">
+        <f>IF(G30="","",COUNTIFS(RawData[Error Type],G30,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J30" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),29),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K30">
+        <f>IF(J30="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J30,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M30" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),29),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N30">
+        <f>IF(M30="","",COUNTIFS(RawData[Severity],M30,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),30),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B31" s="9">
+        <f>IF(A31="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A31,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A31,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D31" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),30),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E31">
+        <f>IF(D31="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D31,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G31" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),30),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H31">
+        <f>IF(G31="","",COUNTIFS(RawData[Error Type],G31,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J31" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),30),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K31">
+        <f>IF(J31="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J31,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M31" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),30),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N31">
+        <f>IF(M31="","",COUNTIFS(RawData[Severity],M31,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),31),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B32" s="9">
+        <f>IF(A32="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A32,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A32,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D32" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),31),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E32">
+        <f>IF(D32="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D32,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G32" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),31),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H32">
+        <f>IF(G32="","",COUNTIFS(RawData[Error Type],G32,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J32" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),31),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K32">
+        <f>IF(J32="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J32,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M32" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),31),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N32">
+        <f>IF(M32="","",COUNTIFS(RawData[Severity],M32,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),32),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B33" s="9">
+        <f>IF(A33="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A33,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A33,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D33" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),32),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E33">
+        <f>IF(D33="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D33,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G33" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),32),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H33">
+        <f>IF(G33="","",COUNTIFS(RawData[Error Type],G33,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J33" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),32),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K33">
+        <f>IF(J33="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J33,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M33" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),32),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N33">
+        <f>IF(M33="","",COUNTIFS(RawData[Severity],M33,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),33),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B34" s="9">
+        <f>IF(A34="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A34,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A34,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D34" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),33),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E34">
+        <f>IF(D34="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D34,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G34" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),33),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H34">
+        <f>IF(G34="","",COUNTIFS(RawData[Error Type],G34,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J34" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),33),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K34">
+        <f>IF(J34="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J34,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M34" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),33),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N34">
+        <f>IF(M34="","",COUNTIFS(RawData[Severity],M34,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),34),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B35" s="9">
+        <f>IF(A35="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A35,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A35,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D35" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),34),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E35">
+        <f>IF(D35="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D35,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G35" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),34),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H35">
+        <f>IF(G35="","",COUNTIFS(RawData[Error Type],G35,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J35" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),34),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K35">
+        <f>IF(J35="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J35,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M35" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),34),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N35">
+        <f>IF(M35="","",COUNTIFS(RawData[Severity],M35,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),35),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B36" s="9">
+        <f>IF(A36="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A36,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A36,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D36" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),35),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E36">
+        <f>IF(D36="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D36,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G36" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),35),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H36">
+        <f>IF(G36="","",COUNTIFS(RawData[Error Type],G36,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J36" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),35),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K36">
+        <f>IF(J36="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J36,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M36" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),35),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N36">
+        <f>IF(M36="","",COUNTIFS(RawData[Severity],M36,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),36),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B37" s="9">
+        <f>IF(A37="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A37,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A37,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D37" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),36),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E37">
+        <f>IF(D37="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D37,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G37" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),36),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H37">
+        <f>IF(G37="","",COUNTIFS(RawData[Error Type],G37,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J37" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),36),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K37">
+        <f>IF(J37="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J37,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M37" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),36),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N37">
+        <f>IF(M37="","",COUNTIFS(RawData[Severity],M37,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),37),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B38" s="9">
+        <f>IF(A38="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A38,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A38,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D38" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),37),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E38">
+        <f>IF(D38="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D38,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G38" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),37),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H38">
+        <f>IF(G38="","",COUNTIFS(RawData[Error Type],G38,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J38" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),37),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K38">
+        <f>IF(J38="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J38,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M38" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),37),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N38">
+        <f>IF(M38="","",COUNTIFS(RawData[Severity],M38,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),38),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B39" s="9">
+        <f>IF(A39="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A39,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A39,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D39" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),38),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E39">
+        <f>IF(D39="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D39,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G39" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),38),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H39">
+        <f>IF(G39="","",COUNTIFS(RawData[Error Type],G39,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J39" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),38),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K39">
+        <f>IF(J39="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J39,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M39" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),38),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N39">
+        <f>IF(M39="","",COUNTIFS(RawData[Severity],M39,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),39),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B40" s="9">
+        <f>IF(A40="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A40,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A40,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D40" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),39),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E40">
+        <f>IF(D40="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D40,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G40" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),39),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H40">
+        <f>IF(G40="","",COUNTIFS(RawData[Error Type],G40,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J40" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),39),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K40">
+        <f>IF(J40="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J40,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M40" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),39),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N40">
+        <f>IF(M40="","",COUNTIFS(RawData[Severity],M40,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),40),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B41" s="9">
+        <f>IF(A41="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A41,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A41,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D41" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),40),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E41">
+        <f>IF(D41="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D41,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G41" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),40),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H41">
+        <f>IF(G41="","",COUNTIFS(RawData[Error Type],G41,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J41" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),40),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K41">
+        <f>IF(J41="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J41,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M41" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),40),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N41">
+        <f>IF(M41="","",COUNTIFS(RawData[Severity],M41,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),41),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B42" s="9">
+        <f>IF(A42="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A42,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A42,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D42" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),41),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E42">
+        <f>IF(D42="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D42,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G42" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),41),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H42">
+        <f>IF(G42="","",COUNTIFS(RawData[Error Type],G42,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J42" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),41),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K42">
+        <f>IF(J42="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J42,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M42" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),41),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N42">
+        <f>IF(M42="","",COUNTIFS(RawData[Severity],M42,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),42),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B43" s="9">
+        <f>IF(A43="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A43,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A43,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D43" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),42),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E43">
+        <f>IF(D43="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D43,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G43" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),42),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H43">
+        <f>IF(G43="","",COUNTIFS(RawData[Error Type],G43,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J43" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),42),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K43">
+        <f>IF(J43="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J43,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M43" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),42),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N43">
+        <f>IF(M43="","",COUNTIFS(RawData[Severity],M43,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),43),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B44" s="9">
+        <f>IF(A44="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A44,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A44,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D44" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),43),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E44">
+        <f>IF(D44="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D44,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G44" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),43),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H44">
+        <f>IF(G44="","",COUNTIFS(RawData[Error Type],G44,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J44" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),43),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K44">
+        <f>IF(J44="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J44,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M44" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),43),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N44">
+        <f>IF(M44="","",COUNTIFS(RawData[Severity],M44,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),44),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B45" s="9">
+        <f>IF(A45="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A45,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A45,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D45" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),44),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E45">
+        <f>IF(D45="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D45,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G45" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),44),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H45">
+        <f>IF(G45="","",COUNTIFS(RawData[Error Type],G45,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J45" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),44),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K45">
+        <f>IF(J45="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J45,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M45" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),44),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N45">
+        <f>IF(M45="","",COUNTIFS(RawData[Severity],M45,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),45),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B46" s="9">
+        <f>IF(A46="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A46,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A46,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D46" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),45),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E46">
+        <f>IF(D46="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D46,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G46" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),45),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H46">
+        <f>IF(G46="","",COUNTIFS(RawData[Error Type],G46,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J46" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),45),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K46">
+        <f>IF(J46="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J46,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M46" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),45),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N46">
+        <f>IF(M46="","",COUNTIFS(RawData[Severity],M46,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),46),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B47" s="9">
+        <f>IF(A47="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A47,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A47,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D47" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),46),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E47">
+        <f>IF(D47="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D47,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G47" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),46),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H47">
+        <f>IF(G47="","",COUNTIFS(RawData[Error Type],G47,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J47" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),46),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K47">
+        <f>IF(J47="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J47,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M47" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),46),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N47">
+        <f>IF(M47="","",COUNTIFS(RawData[Severity],M47,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),47),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B48" s="9">
+        <f>IF(A48="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A48,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A48,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D48" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),47),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E48">
+        <f>IF(D48="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D48,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G48" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),47),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H48">
+        <f>IF(G48="","",COUNTIFS(RawData[Error Type],G48,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J48" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),47),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K48">
+        <f>IF(J48="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J48,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M48" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),47),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N48">
+        <f>IF(M48="","",COUNTIFS(RawData[Severity],M48,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),48),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B49" s="9">
+        <f>IF(A49="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A49,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A49,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D49" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),48),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E49">
+        <f>IF(D49="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D49,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G49" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),48),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H49">
+        <f>IF(G49="","",COUNTIFS(RawData[Error Type],G49,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J49" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),48),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K49">
+        <f>IF(J49="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J49,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M49" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),48),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N49">
+        <f>IF(M49="","",COUNTIFS(RawData[Severity],M49,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),49),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B50" s="9">
+        <f>IF(A50="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A50,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A50,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D50" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),49),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E50">
+        <f>IF(D50="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D50,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G50" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),49),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H50">
+        <f>IF(G50="","",COUNTIFS(RawData[Error Type],G50,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J50" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),49),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K50">
+        <f>IF(J50="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J50,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M50" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),49),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N50">
+        <f>IF(M50="","",COUNTIFS(RawData[Severity],M50,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),50),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="B51" s="9">
+        <f>IF(A51="","",IFERROR(MAX(0,1-SUMIFS(RawData[Error Flag],RawData[Telecaller Name],A51,RawData[RowVis],1)/COUNTIFS(RawData[Telecaller Name],A51,RawData[RowVis],1)),0))</f>
+        <v>0</v>
+      </c>
+      <c r="D51" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Telecaller Name],(RawData[Telecaller Name]&lt;&gt;"")*(RawData[RowVis]=1))),50),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="E51">
+        <f>IF(D51="","",SUMIFS(RawData[Error Flag],RawData[Telecaller Name],D51,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="G51" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Error Type],(RawData[Error Type]&lt;&gt;"")*(RawData[Error Type]&lt;&gt;"None")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),50),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="H51">
+        <f>IF(G51="","",COUNTIFS(RawData[Error Type],G51,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="J51" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Project Name],(RawData[Project Name]&lt;&gt;"")*(RawData[RowVis]=1)*(RawData[Error Flag]&gt;0))),50),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="K51">
+        <f>IF(J51="","",SUMIFS(RawData[Error Flag],RawData[Project Name],J51,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+      <c r="M51" t="str">
+        <f>IFERROR(INDEX(_xlfn.UNIQUE(_xlfn._xlws.FILTER(RawData[Severity],(RawData[Severity]&lt;&gt;"")*(RawData[RowVis]=1))),50),_xlfn.NA())</f>
+        <v/>
+      </c>
+      <c r="N51">
+        <f>IF(M51="","",COUNTIFS(RawData[Severity],M51,RawData[RowVis],1))</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
